--- a/Электрические машины/Практика/Book4.xlsx
+++ b/Электрические машины/Практика/Book4.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Github\Course3\Электрические машины\Практика\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4DFA5FC-FBED-4113-BD56-70C0DA519F89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6725E034-845C-4CC4-9954-B54D68C83EF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{A2D4E568-549A-4935-B465-6E79E9C6F364}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14400" windowHeight="16200" xr2:uid="{A2D4E568-549A-4935-B465-6E79E9C6F364}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -297,7 +297,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -309,18 +309,8 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -329,10 +319,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -798,17 +794,17 @@
         <v>213.92</v>
       </c>
       <c r="C15">
-        <v>1359</v>
+        <v>1089</v>
       </c>
       <c r="E15" t="s">
         <v>12</v>
       </c>
-      <c r="F15" s="8" t="s">
+      <c r="F15" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G15" s="14">
+      <c r="G15" s="9">
         <f>(B15*C15)/9.55</f>
-        <v>30441.599999999995</v>
+        <v>24393.599999999995</v>
       </c>
     </row>
     <row r="16" spans="2:15" x14ac:dyDescent="0.25">
@@ -817,64 +813,58 @@
       </c>
       <c r="O16">
         <f>G15+L13</f>
-        <v>33092.718196235997</v>
+        <v>27044.718196235994</v>
       </c>
     </row>
     <row r="17" spans="3:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I17" s="7"/>
-      <c r="J17" s="7"/>
-      <c r="K17" s="7"/>
-      <c r="S17" s="11"/>
+      <c r="S17" s="7"/>
     </row>
     <row r="18" spans="3:19" x14ac:dyDescent="0.25">
-      <c r="E18" s="5" t="s">
+      <c r="E18" s="10" t="s">
         <v>8</v>
       </c>
       <c r="F18" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="G18" s="5" t="s">
+      <c r="G18" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="H18" s="5">
-        <f>G15/(G15+J11)*100</f>
-        <v>100</v>
-      </c>
-      <c r="I18" s="7"/>
-      <c r="J18" s="7"/>
-      <c r="K18" s="7"/>
+      <c r="H18" s="10">
+        <f>G15/(G15+L13)*100</f>
+        <v>90.197279272797246</v>
+      </c>
     </row>
     <row r="19" spans="3:19" x14ac:dyDescent="0.25">
-      <c r="E19" s="5"/>
+      <c r="E19" s="10"/>
       <c r="F19" t="s">
         <v>11</v>
       </c>
-      <c r="G19" s="5"/>
-      <c r="H19" s="5"/>
+      <c r="G19" s="10"/>
+      <c r="H19" s="10"/>
     </row>
     <row r="20" spans="3:19" x14ac:dyDescent="0.25">
       <c r="H20" s="1"/>
-      <c r="L20" s="9" t="s">
+      <c r="L20" s="12" t="s">
         <v>8</v>
       </c>
       <c r="M20" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="N20" s="5" t="s">
+      <c r="N20" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="O20" s="6">
+      <c r="O20" s="11">
         <f>(G15/(G15*L13))*100</f>
         <v>3.7719932721965325E-2</v>
       </c>
     </row>
     <row r="21" spans="3:19" x14ac:dyDescent="0.25">
-      <c r="L21" s="9"/>
+      <c r="L21" s="12"/>
       <c r="M21" t="s">
         <v>30</v>
       </c>
-      <c r="N21" s="5"/>
-      <c r="O21" s="6"/>
+      <c r="N21" s="10"/>
+      <c r="O21" s="11"/>
     </row>
     <row r="22" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C22" t="s">
@@ -923,7 +913,7 @@
       <c r="I23">
         <v>0.93</v>
       </c>
-      <c r="L23" s="10" t="s">
+      <c r="L23" s="6" t="s">
         <v>20</v>
       </c>
       <c r="M23">
@@ -933,17 +923,7 @@
       <c r="N23" t="s">
         <v>21</v>
       </c>
-      <c r="O23" s="11"/>
-    </row>
-    <row r="24" spans="3:19" x14ac:dyDescent="0.25">
-      <c r="J24" s="7"/>
-      <c r="K24" s="7"/>
-      <c r="L24" s="7"/>
-      <c r="M24" s="7"/>
-      <c r="N24" s="7"/>
-      <c r="O24" s="7"/>
-      <c r="P24" s="7"/>
-      <c r="Q24" s="7"/>
+      <c r="O23" s="7"/>
     </row>
     <row r="25" spans="3:19" x14ac:dyDescent="0.25">
       <c r="D25" s="1"/>
@@ -968,49 +948,49 @@
       <c r="I26" s="1"/>
       <c r="J26" s="1"/>
       <c r="K26" s="1"/>
-      <c r="L26" s="9" t="s">
+      <c r="L26" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="M26" s="12" t="s">
+      <c r="M26" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="N26" s="5" t="s">
+      <c r="N26" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="O26" s="5">
+      <c r="O26" s="10">
         <f>(B15*C15)/9.55</f>
-        <v>30441.599999999995</v>
+        <v>24393.599999999995</v>
       </c>
     </row>
     <row r="27" spans="3:19" x14ac:dyDescent="0.25">
-      <c r="L27" s="9"/>
+      <c r="L27" s="12"/>
       <c r="M27" s="3">
         <v>9.5500000000000007</v>
       </c>
-      <c r="N27" s="5"/>
-      <c r="O27" s="5"/>
+      <c r="N27" s="10"/>
+      <c r="O27" s="10"/>
     </row>
     <row r="29" spans="3:19" x14ac:dyDescent="0.25">
-      <c r="M29" s="13"/>
-      <c r="N29" s="13"/>
-      <c r="O29" s="13"/>
+      <c r="M29" s="1"/>
+      <c r="N29" s="1"/>
+      <c r="O29" s="1"/>
     </row>
     <row r="30" spans="3:19" x14ac:dyDescent="0.25">
-      <c r="M30" s="13"/>
-      <c r="N30" s="13"/>
-      <c r="O30" s="13"/>
+      <c r="M30" s="1"/>
+      <c r="N30" s="1"/>
+      <c r="O30" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="E18:E19"/>
+    <mergeCell ref="G18:G19"/>
+    <mergeCell ref="H18:H19"/>
     <mergeCell ref="N20:N21"/>
     <mergeCell ref="O20:O21"/>
     <mergeCell ref="L20:L21"/>
     <mergeCell ref="O26:O27"/>
     <mergeCell ref="N26:N27"/>
     <mergeCell ref="L26:L27"/>
-    <mergeCell ref="E18:E19"/>
-    <mergeCell ref="G18:G19"/>
-    <mergeCell ref="H18:H19"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
